--- a/hall/resources/sample/UpcomingMobileGame.xlsx
+++ b/hall/resources/sample/UpcomingMobileGame.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12255"/>
+    <workbookView windowWidth="27945" windowHeight="12375"/>
   </bookViews>
   <sheets>
     <sheet name="UpcomingMobileGame" sheetId="1" r:id="rId1"/>
@@ -52,7 +52,8 @@
             <charset val="134"/>
           </rPr>
           <t xml:space="preserve">
-0表示显示，1表示不显示</t>
+TRUE表示显示，FALSE
+表示不显示</t>
         </r>
       </text>
     </comment>
@@ -61,7 +62,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="64" uniqueCount="62">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="112" uniqueCount="110">
   <si>
     <t>游戏id</t>
   </si>
@@ -72,7 +73,7 @@
     <t>游戏图片资源名</t>
   </si>
   <si>
-    <t>游戏名称资源名</t>
+    <t>游戏名称多语言</t>
   </si>
   <si>
     <t>描述多语言ID</t>
@@ -96,157 +97,301 @@
     <t>picture</t>
   </si>
   <si>
-    <t>icon</t>
+    <t>name</t>
   </si>
   <si>
     <t>text</t>
   </si>
   <si>
-    <t>open</t>
+    <t>display</t>
   </si>
   <si>
     <t>捕鱼大亨</t>
   </si>
   <si>
+    <t>yxqdb_tu_2</t>
+  </si>
+  <si>
     <t>抢庄牛牛</t>
   </si>
   <si>
+    <t>yxqdb_tu_3</t>
+  </si>
+  <si>
     <t>百人牛牛</t>
   </si>
   <si>
+    <t>yxqdb_tu_4</t>
+  </si>
+  <si>
     <t>通比牛牛</t>
   </si>
   <si>
+    <t>yxqdb_tu_5</t>
+  </si>
+  <si>
     <t>小鸡冲刺</t>
   </si>
   <si>
+    <t>yxqdb_tu_6</t>
+  </si>
+  <si>
     <t>DOUBLE</t>
   </si>
   <si>
+    <t>yxqdb_tu_7</t>
+  </si>
+  <si>
     <t>FAST PARITY</t>
   </si>
   <si>
+    <t>yxqdb_tu_8</t>
+  </si>
+  <si>
     <t>德古拉之黑暗财富</t>
   </si>
   <si>
+    <t>yxqdb_tu_9</t>
+  </si>
+  <si>
     <t>招财喵</t>
   </si>
   <si>
+    <t>yxqdb_tu_10</t>
+  </si>
+  <si>
     <t>澳门壕梦</t>
   </si>
   <si>
+    <t>yxqdb_tu_11</t>
+  </si>
+  <si>
     <t>比基尼天堂</t>
   </si>
   <si>
+    <t>yxqdb_tu_12</t>
+  </si>
+  <si>
     <t>超级高尔夫</t>
   </si>
   <si>
+    <t>yxqdb_tu_13</t>
+  </si>
+  <si>
     <t>夜醉佳人</t>
   </si>
   <si>
+    <t>yxqdb_tu_14</t>
+  </si>
+  <si>
     <t>复活节的惊喜</t>
   </si>
   <si>
+    <t>yxqdb_tu_15</t>
+  </si>
+  <si>
     <t>相扑之王</t>
   </si>
   <si>
+    <t>yxqdb_tu_16</t>
+  </si>
+  <si>
     <t>嗨到底</t>
   </si>
   <si>
+    <t>yxqdb_tu_17</t>
+  </si>
+  <si>
     <t>狂野沙滩</t>
   </si>
   <si>
+    <t>yxqdb_tu_18</t>
+  </si>
+  <si>
     <t>最终幻想</t>
   </si>
   <si>
+    <t>yxqdb_tu_19</t>
+  </si>
+  <si>
     <t>万圣狂欢夜</t>
   </si>
   <si>
+    <t>yxqdb_tu_20</t>
+  </si>
+  <si>
     <t>水果丛林</t>
   </si>
   <si>
+    <t>yxqdb_tu_21</t>
+  </si>
+  <si>
     <t>功夫虎</t>
   </si>
   <si>
+    <t>yxqdb_tu_22</t>
+  </si>
+  <si>
     <t>麻将胡了2</t>
   </si>
   <si>
+    <t>yxqdb_tu_23</t>
+  </si>
+  <si>
     <t>黄金帝国</t>
   </si>
   <si>
+    <t>yxqdb_tu_24</t>
+  </si>
+  <si>
     <t>伽罗宝石</t>
   </si>
   <si>
+    <t>yxqdb_tu_25</t>
+  </si>
+  <si>
     <t>伽罗宝石2</t>
   </si>
   <si>
+    <t>yxqdb_tu_26</t>
+  </si>
+  <si>
     <t>伽罗宝石3</t>
   </si>
   <si>
+    <t>yxqdb_tu_27</t>
+  </si>
+  <si>
     <t>赏金大对决</t>
   </si>
   <si>
+    <t>yxqdb_tu_28</t>
+  </si>
+  <si>
     <t>极速糖果1000</t>
   </si>
   <si>
+    <t>yxqdb_tu_29</t>
+  </si>
+  <si>
     <t>奥林匹斯之门1000</t>
   </si>
   <si>
+    <t>yxqdb_tu_30</t>
+  </si>
+  <si>
     <t>奥林匹斯之门超神力</t>
   </si>
   <si>
+    <t>yxqdb_tu_31</t>
+  </si>
+  <si>
     <t>幸运狮子</t>
   </si>
   <si>
+    <t>yxqdb_tu_32</t>
+  </si>
+  <si>
     <t>海盗女王</t>
   </si>
   <si>
+    <t>yxqdb_tu_33</t>
+  </si>
+  <si>
     <t>龙息之焰</t>
   </si>
   <si>
+    <t>yxqdb_tu_34</t>
+  </si>
+  <si>
     <t>黑神话·天命人</t>
   </si>
   <si>
+    <t>yxqdb_tu_35</t>
+  </si>
+  <si>
     <t>混沌·神魔之战</t>
   </si>
   <si>
+    <t>yxqdb_tu_36</t>
+  </si>
+  <si>
     <t>白羊座荣耀</t>
   </si>
   <si>
+    <t>yxqdb_tu_37</t>
+  </si>
+  <si>
     <t>天蝎秘宝</t>
   </si>
   <si>
+    <t>yxqdb_tu_38</t>
+  </si>
+  <si>
     <t>狮子座传说</t>
   </si>
   <si>
+    <t>yxqdb_tu_39</t>
+  </si>
+  <si>
     <t>神之守护者</t>
   </si>
   <si>
+    <t>yxqdb_tu_40</t>
+  </si>
+  <si>
     <t>小丑派对</t>
   </si>
   <si>
+    <t>yxqdb_tu_41</t>
+  </si>
+  <si>
     <t>马里奥赛车</t>
   </si>
   <si>
+    <t>yxqdb_tu_42</t>
+  </si>
+  <si>
     <t>双面女王</t>
   </si>
   <si>
+    <t>yxqdb_tu_43</t>
+  </si>
+  <si>
     <t>寻宝俏丽人</t>
   </si>
   <si>
+    <t>yxqdb_tu_44</t>
+  </si>
+  <si>
     <t>蜘蛛侠</t>
   </si>
   <si>
+    <t>yxqdb_tu_45</t>
+  </si>
+  <si>
     <t>植物vs僵尸</t>
   </si>
   <si>
+    <t>yxqdb_tu_46</t>
+  </si>
+  <si>
     <t>钢铁侠</t>
   </si>
   <si>
+    <t>yxqdb_tu_47</t>
+  </si>
+  <si>
     <t>绝地求生</t>
   </si>
   <si>
+    <t>yxqdb_tu_48</t>
+  </si>
+  <si>
     <t>复仇者联盟</t>
+  </si>
+  <si>
+    <t>yxqdb_tu_49</t>
   </si>
 </sst>
 </file>
@@ -418,12 +563,12 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
+      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
@@ -1251,8 +1396,8 @@
       <c r="C2" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="D2" s="1" t="s">
-        <v>7</v>
+      <c r="D2" s="2" t="s">
+        <v>6</v>
       </c>
       <c r="E2" s="2" t="s">
         <v>6</v>
@@ -1285,6 +1430,12 @@
       <c r="B5" s="1" t="s">
         <v>14</v>
       </c>
+      <c r="C5" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="D5" s="1">
+        <v>44052</v>
+      </c>
       <c r="E5" s="1">
         <v>44002</v>
       </c>
@@ -1297,7 +1448,13 @@
         <v>2</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="D6" s="1">
+        <v>44053</v>
       </c>
       <c r="E6" s="1">
         <v>44003</v>
@@ -1311,7 +1468,13 @@
         <v>3</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>16</v>
+        <v>18</v>
+      </c>
+      <c r="C7" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="D7" s="1">
+        <v>44054</v>
       </c>
       <c r="E7" s="1">
         <v>44004</v>
@@ -1325,7 +1488,13 @@
         <v>4</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>17</v>
+        <v>20</v>
+      </c>
+      <c r="C8" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="D8" s="1">
+        <v>44055</v>
       </c>
       <c r="E8" s="1">
         <v>44005</v>
@@ -1339,7 +1508,13 @@
         <v>5</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>18</v>
+        <v>22</v>
+      </c>
+      <c r="C9" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="D9" s="1">
+        <v>44056</v>
       </c>
       <c r="E9" s="1">
         <v>44006</v>
@@ -1353,7 +1528,13 @@
         <v>6</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>19</v>
+        <v>24</v>
+      </c>
+      <c r="C10" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="D10" s="1">
+        <v>44057</v>
       </c>
       <c r="E10" s="1">
         <v>44007</v>
@@ -1367,7 +1548,13 @@
         <v>7</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>20</v>
+        <v>26</v>
+      </c>
+      <c r="C11" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="D11" s="1">
+        <v>44058</v>
       </c>
       <c r="E11" s="1">
         <v>44008</v>
@@ -1381,7 +1568,13 @@
         <v>8</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>21</v>
+        <v>28</v>
+      </c>
+      <c r="C12" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="D12" s="1">
+        <v>44059</v>
       </c>
       <c r="E12" s="1">
         <v>44009</v>
@@ -1395,7 +1588,13 @@
         <v>9</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>22</v>
+        <v>30</v>
+      </c>
+      <c r="C13" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="D13" s="1">
+        <v>44060</v>
       </c>
       <c r="E13" s="1">
         <v>44010</v>
@@ -1409,7 +1608,13 @@
         <v>10</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>23</v>
+        <v>32</v>
+      </c>
+      <c r="C14" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="D14" s="1">
+        <v>44061</v>
       </c>
       <c r="E14" s="1">
         <v>44011</v>
@@ -1423,7 +1628,13 @@
         <v>11</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>24</v>
+        <v>34</v>
+      </c>
+      <c r="C15" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="D15" s="1">
+        <v>44062</v>
       </c>
       <c r="E15" s="1">
         <v>44012</v>
@@ -1437,7 +1648,13 @@
         <v>12</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>25</v>
+        <v>36</v>
+      </c>
+      <c r="C16" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="D16" s="1">
+        <v>44063</v>
       </c>
       <c r="E16" s="1">
         <v>44013</v>
@@ -1451,7 +1668,13 @@
         <v>13</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>26</v>
+        <v>38</v>
+      </c>
+      <c r="C17" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="D17" s="1">
+        <v>44064</v>
       </c>
       <c r="E17" s="1">
         <v>44014</v>
@@ -1465,7 +1688,13 @@
         <v>14</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>27</v>
+        <v>40</v>
+      </c>
+      <c r="C18" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="D18" s="1">
+        <v>44065</v>
       </c>
       <c r="E18" s="1">
         <v>44015</v>
@@ -1479,7 +1708,13 @@
         <v>15</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>28</v>
+        <v>42</v>
+      </c>
+      <c r="C19" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="D19" s="1">
+        <v>44066</v>
       </c>
       <c r="E19" s="1">
         <v>44016</v>
@@ -1493,7 +1728,13 @@
         <v>16</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>29</v>
+        <v>44</v>
+      </c>
+      <c r="C20" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="D20" s="1">
+        <v>44067</v>
       </c>
       <c r="E20" s="1">
         <v>44017</v>
@@ -1507,7 +1748,13 @@
         <v>17</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>30</v>
+        <v>46</v>
+      </c>
+      <c r="C21" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="D21" s="1">
+        <v>44068</v>
       </c>
       <c r="E21" s="1">
         <v>44018</v>
@@ -1521,7 +1768,13 @@
         <v>18</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>31</v>
+        <v>48</v>
+      </c>
+      <c r="C22" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="D22" s="1">
+        <v>44069</v>
       </c>
       <c r="E22" s="1">
         <v>44019</v>
@@ -1535,7 +1788,13 @@
         <v>19</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>32</v>
+        <v>50</v>
+      </c>
+      <c r="C23" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="D23" s="1">
+        <v>44070</v>
       </c>
       <c r="E23" s="1">
         <v>44020</v>
@@ -1549,7 +1808,13 @@
         <v>20</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>33</v>
+        <v>52</v>
+      </c>
+      <c r="C24" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="D24" s="1">
+        <v>44071</v>
       </c>
       <c r="E24" s="1">
         <v>44021</v>
@@ -1563,7 +1828,13 @@
         <v>21</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>34</v>
+        <v>54</v>
+      </c>
+      <c r="C25" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="D25" s="1">
+        <v>44072</v>
       </c>
       <c r="E25" s="1">
         <v>44022</v>
@@ -1577,7 +1848,13 @@
         <v>22</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>35</v>
+        <v>56</v>
+      </c>
+      <c r="C26" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="D26" s="1">
+        <v>44073</v>
       </c>
       <c r="E26" s="1">
         <v>44023</v>
@@ -1591,7 +1868,13 @@
         <v>23</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>36</v>
+        <v>58</v>
+      </c>
+      <c r="C27" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="D27" s="1">
+        <v>44074</v>
       </c>
       <c r="E27" s="1">
         <v>44024</v>
@@ -1605,7 +1888,13 @@
         <v>24</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>37</v>
+        <v>60</v>
+      </c>
+      <c r="C28" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="D28" s="1">
+        <v>44075</v>
       </c>
       <c r="E28" s="1">
         <v>44025</v>
@@ -1619,7 +1908,13 @@
         <v>25</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>38</v>
+        <v>62</v>
+      </c>
+      <c r="C29" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="D29" s="1">
+        <v>44076</v>
       </c>
       <c r="E29" s="1">
         <v>44026</v>
@@ -1633,7 +1928,13 @@
         <v>26</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>39</v>
+        <v>64</v>
+      </c>
+      <c r="C30" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="D30" s="1">
+        <v>44077</v>
       </c>
       <c r="E30" s="1">
         <v>44027</v>
@@ -1647,7 +1948,13 @@
         <v>27</v>
       </c>
       <c r="B31" s="1" t="s">
-        <v>40</v>
+        <v>66</v>
+      </c>
+      <c r="C31" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="D31" s="1">
+        <v>44078</v>
       </c>
       <c r="E31" s="1">
         <v>44028</v>
@@ -1661,7 +1968,13 @@
         <v>28</v>
       </c>
       <c r="B32" s="1" t="s">
-        <v>41</v>
+        <v>68</v>
+      </c>
+      <c r="C32" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="D32" s="1">
+        <v>44079</v>
       </c>
       <c r="E32" s="1">
         <v>44029</v>
@@ -1675,7 +1988,13 @@
         <v>29</v>
       </c>
       <c r="B33" s="1" t="s">
-        <v>42</v>
+        <v>70</v>
+      </c>
+      <c r="C33" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="D33" s="1">
+        <v>44080</v>
       </c>
       <c r="E33" s="1">
         <v>44030</v>
@@ -1689,7 +2008,13 @@
         <v>30</v>
       </c>
       <c r="B34" s="1" t="s">
-        <v>43</v>
+        <v>72</v>
+      </c>
+      <c r="C34" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="D34" s="1">
+        <v>44081</v>
       </c>
       <c r="E34" s="1">
         <v>44031</v>
@@ -1703,7 +2028,13 @@
         <v>31</v>
       </c>
       <c r="B35" s="1" t="s">
-        <v>44</v>
+        <v>74</v>
+      </c>
+      <c r="C35" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="D35" s="1">
+        <v>44082</v>
       </c>
       <c r="E35" s="1">
         <v>44032</v>
@@ -1717,7 +2048,13 @@
         <v>32</v>
       </c>
       <c r="B36" s="1" t="s">
-        <v>45</v>
+        <v>76</v>
+      </c>
+      <c r="C36" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="D36" s="1">
+        <v>44083</v>
       </c>
       <c r="E36" s="1">
         <v>44033</v>
@@ -1731,7 +2068,13 @@
         <v>33</v>
       </c>
       <c r="B37" s="1" t="s">
-        <v>46</v>
+        <v>78</v>
+      </c>
+      <c r="C37" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="D37" s="1">
+        <v>44084</v>
       </c>
       <c r="E37" s="1">
         <v>44034</v>
@@ -1745,7 +2088,13 @@
         <v>34</v>
       </c>
       <c r="B38" s="1" t="s">
-        <v>47</v>
+        <v>80</v>
+      </c>
+      <c r="C38" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="D38" s="1">
+        <v>44085</v>
       </c>
       <c r="E38" s="1">
         <v>44035</v>
@@ -1759,7 +2108,13 @@
         <v>35</v>
       </c>
       <c r="B39" s="1" t="s">
-        <v>48</v>
+        <v>82</v>
+      </c>
+      <c r="C39" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="D39" s="1">
+        <v>44086</v>
       </c>
       <c r="E39" s="1">
         <v>44036</v>
@@ -1773,7 +2128,13 @@
         <v>36</v>
       </c>
       <c r="B40" s="1" t="s">
-        <v>49</v>
+        <v>84</v>
+      </c>
+      <c r="C40" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="D40" s="1">
+        <v>44087</v>
       </c>
       <c r="E40" s="1">
         <v>44037</v>
@@ -1787,7 +2148,13 @@
         <v>37</v>
       </c>
       <c r="B41" s="1" t="s">
-        <v>50</v>
+        <v>86</v>
+      </c>
+      <c r="C41" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="D41" s="1">
+        <v>44088</v>
       </c>
       <c r="E41" s="1">
         <v>44038</v>
@@ -1801,7 +2168,13 @@
         <v>38</v>
       </c>
       <c r="B42" s="1" t="s">
-        <v>51</v>
+        <v>88</v>
+      </c>
+      <c r="C42" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="D42" s="1">
+        <v>44089</v>
       </c>
       <c r="E42" s="1">
         <v>44039</v>
@@ -1815,7 +2188,13 @@
         <v>39</v>
       </c>
       <c r="B43" s="1" t="s">
-        <v>52</v>
+        <v>90</v>
+      </c>
+      <c r="C43" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="D43" s="1">
+        <v>44090</v>
       </c>
       <c r="E43" s="1">
         <v>44040</v>
@@ -1829,7 +2208,13 @@
         <v>40</v>
       </c>
       <c r="B44" s="1" t="s">
-        <v>53</v>
+        <v>92</v>
+      </c>
+      <c r="C44" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="D44" s="1">
+        <v>44091</v>
       </c>
       <c r="E44" s="1">
         <v>44041</v>
@@ -1843,7 +2228,13 @@
         <v>41</v>
       </c>
       <c r="B45" s="1" t="s">
-        <v>54</v>
+        <v>94</v>
+      </c>
+      <c r="C45" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="D45" s="1">
+        <v>44092</v>
       </c>
       <c r="E45" s="1">
         <v>44042</v>
@@ -1857,7 +2248,13 @@
         <v>42</v>
       </c>
       <c r="B46" s="1" t="s">
-        <v>55</v>
+        <v>96</v>
+      </c>
+      <c r="C46" s="1" t="s">
+        <v>97</v>
+      </c>
+      <c r="D46" s="1">
+        <v>44093</v>
       </c>
       <c r="E46" s="1">
         <v>44043</v>
@@ -1871,7 +2268,13 @@
         <v>43</v>
       </c>
       <c r="B47" s="1" t="s">
-        <v>56</v>
+        <v>98</v>
+      </c>
+      <c r="C47" s="1" t="s">
+        <v>99</v>
+      </c>
+      <c r="D47" s="1">
+        <v>44094</v>
       </c>
       <c r="E47" s="1">
         <v>44044</v>
@@ -1885,7 +2288,13 @@
         <v>44</v>
       </c>
       <c r="B48" s="1" t="s">
-        <v>57</v>
+        <v>100</v>
+      </c>
+      <c r="C48" s="1" t="s">
+        <v>101</v>
+      </c>
+      <c r="D48" s="1">
+        <v>44095</v>
       </c>
       <c r="E48" s="1">
         <v>44045</v>
@@ -1899,7 +2308,13 @@
         <v>45</v>
       </c>
       <c r="B49" s="1" t="s">
-        <v>58</v>
+        <v>102</v>
+      </c>
+      <c r="C49" s="1" t="s">
+        <v>103</v>
+      </c>
+      <c r="D49" s="1">
+        <v>44096</v>
       </c>
       <c r="E49" s="1">
         <v>44046</v>
@@ -1913,7 +2328,13 @@
         <v>46</v>
       </c>
       <c r="B50" s="1" t="s">
-        <v>59</v>
+        <v>104</v>
+      </c>
+      <c r="C50" s="1" t="s">
+        <v>105</v>
+      </c>
+      <c r="D50" s="1">
+        <v>44097</v>
       </c>
       <c r="E50" s="1">
         <v>44047</v>
@@ -1927,7 +2348,13 @@
         <v>47</v>
       </c>
       <c r="B51" s="1" t="s">
-        <v>60</v>
+        <v>106</v>
+      </c>
+      <c r="C51" s="1" t="s">
+        <v>107</v>
+      </c>
+      <c r="D51" s="1">
+        <v>44098</v>
       </c>
       <c r="E51" s="1">
         <v>44048</v>
@@ -1941,7 +2368,13 @@
         <v>48</v>
       </c>
       <c r="B52" s="1" t="s">
-        <v>61</v>
+        <v>108</v>
+      </c>
+      <c r="C52" s="1" t="s">
+        <v>109</v>
+      </c>
+      <c r="D52" s="1">
+        <v>44099</v>
       </c>
       <c r="E52" s="1">
         <v>44049</v>

--- a/hall/resources/sample/UpcomingMobileGame.xlsx
+++ b/hall/resources/sample/UpcomingMobileGame.xlsx
@@ -52,7 +52,8 @@
             <charset val="134"/>
           </rPr>
           <t xml:space="preserve">
-0表示显示，1表示不显示</t>
+TRUE表示显示，FALSE
+表示不显示</t>
         </r>
       </text>
     </comment>
@@ -61,7 +62,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="62" uniqueCount="60">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="112" uniqueCount="110">
   <si>
     <t>游戏id</t>
   </si>
@@ -72,7 +73,7 @@
     <t>游戏图片资源名</t>
   </si>
   <si>
-    <t>游戏名称资源名</t>
+    <t>游戏名称多语言</t>
   </si>
   <si>
     <t>描述多语言ID</t>
@@ -87,160 +88,310 @@
     <t>string</t>
   </si>
   <si>
+    <t>bool</t>
+  </si>
+  <si>
     <t>id</t>
   </si>
   <si>
     <t>picture</t>
   </si>
   <si>
-    <t>icon</t>
+    <t>name</t>
   </si>
   <si>
     <t>text</t>
   </si>
   <si>
+    <t>display</t>
+  </si>
+  <si>
     <t>捕鱼大亨</t>
   </si>
   <si>
+    <t>yxqdb_tu_2</t>
+  </si>
+  <si>
     <t>抢庄牛牛</t>
   </si>
   <si>
+    <t>yxqdb_tu_3</t>
+  </si>
+  <si>
     <t>百人牛牛</t>
   </si>
   <si>
+    <t>yxqdb_tu_4</t>
+  </si>
+  <si>
     <t>通比牛牛</t>
   </si>
   <si>
+    <t>yxqdb_tu_5</t>
+  </si>
+  <si>
     <t>小鸡冲刺</t>
   </si>
   <si>
+    <t>yxqdb_tu_6</t>
+  </si>
+  <si>
     <t>DOUBLE</t>
   </si>
   <si>
+    <t>yxqdb_tu_7</t>
+  </si>
+  <si>
     <t>FAST PARITY</t>
   </si>
   <si>
+    <t>yxqdb_tu_8</t>
+  </si>
+  <si>
     <t>德古拉之黑暗财富</t>
   </si>
   <si>
+    <t>yxqdb_tu_9</t>
+  </si>
+  <si>
     <t>招财喵</t>
   </si>
   <si>
+    <t>yxqdb_tu_10</t>
+  </si>
+  <si>
     <t>澳门壕梦</t>
   </si>
   <si>
+    <t>yxqdb_tu_11</t>
+  </si>
+  <si>
     <t>比基尼天堂</t>
   </si>
   <si>
+    <t>yxqdb_tu_12</t>
+  </si>
+  <si>
     <t>超级高尔夫</t>
   </si>
   <si>
+    <t>yxqdb_tu_13</t>
+  </si>
+  <si>
     <t>夜醉佳人</t>
   </si>
   <si>
+    <t>yxqdb_tu_14</t>
+  </si>
+  <si>
     <t>复活节的惊喜</t>
   </si>
   <si>
+    <t>yxqdb_tu_15</t>
+  </si>
+  <si>
     <t>相扑之王</t>
   </si>
   <si>
+    <t>yxqdb_tu_16</t>
+  </si>
+  <si>
     <t>嗨到底</t>
   </si>
   <si>
+    <t>yxqdb_tu_17</t>
+  </si>
+  <si>
     <t>狂野沙滩</t>
   </si>
   <si>
+    <t>yxqdb_tu_18</t>
+  </si>
+  <si>
     <t>最终幻想</t>
   </si>
   <si>
+    <t>yxqdb_tu_19</t>
+  </si>
+  <si>
     <t>万圣狂欢夜</t>
   </si>
   <si>
+    <t>yxqdb_tu_20</t>
+  </si>
+  <si>
     <t>水果丛林</t>
   </si>
   <si>
+    <t>yxqdb_tu_21</t>
+  </si>
+  <si>
     <t>功夫虎</t>
   </si>
   <si>
+    <t>yxqdb_tu_22</t>
+  </si>
+  <si>
     <t>麻将胡了2</t>
   </si>
   <si>
+    <t>yxqdb_tu_23</t>
+  </si>
+  <si>
     <t>黄金帝国</t>
   </si>
   <si>
+    <t>yxqdb_tu_24</t>
+  </si>
+  <si>
     <t>伽罗宝石</t>
   </si>
   <si>
+    <t>yxqdb_tu_25</t>
+  </si>
+  <si>
     <t>伽罗宝石2</t>
   </si>
   <si>
+    <t>yxqdb_tu_26</t>
+  </si>
+  <si>
     <t>伽罗宝石3</t>
   </si>
   <si>
+    <t>yxqdb_tu_27</t>
+  </si>
+  <si>
     <t>赏金大对决</t>
   </si>
   <si>
+    <t>yxqdb_tu_28</t>
+  </si>
+  <si>
     <t>极速糖果1000</t>
   </si>
   <si>
+    <t>yxqdb_tu_29</t>
+  </si>
+  <si>
     <t>奥林匹斯之门1000</t>
   </si>
   <si>
+    <t>yxqdb_tu_30</t>
+  </si>
+  <si>
     <t>奥林匹斯之门超神力</t>
   </si>
   <si>
+    <t>yxqdb_tu_31</t>
+  </si>
+  <si>
     <t>幸运狮子</t>
   </si>
   <si>
+    <t>yxqdb_tu_32</t>
+  </si>
+  <si>
     <t>海盗女王</t>
   </si>
   <si>
+    <t>yxqdb_tu_33</t>
+  </si>
+  <si>
     <t>龙息之焰</t>
   </si>
   <si>
+    <t>yxqdb_tu_34</t>
+  </si>
+  <si>
     <t>黑神话·天命人</t>
   </si>
   <si>
+    <t>yxqdb_tu_35</t>
+  </si>
+  <si>
     <t>混沌·神魔之战</t>
   </si>
   <si>
+    <t>yxqdb_tu_36</t>
+  </si>
+  <si>
     <t>白羊座荣耀</t>
   </si>
   <si>
+    <t>yxqdb_tu_37</t>
+  </si>
+  <si>
     <t>天蝎秘宝</t>
   </si>
   <si>
+    <t>yxqdb_tu_38</t>
+  </si>
+  <si>
     <t>狮子座传说</t>
   </si>
   <si>
+    <t>yxqdb_tu_39</t>
+  </si>
+  <si>
     <t>神之守护者</t>
   </si>
   <si>
+    <t>yxqdb_tu_40</t>
+  </si>
+  <si>
     <t>小丑派对</t>
   </si>
   <si>
+    <t>yxqdb_tu_41</t>
+  </si>
+  <si>
     <t>马里奥赛车</t>
   </si>
   <si>
+    <t>yxqdb_tu_42</t>
+  </si>
+  <si>
     <t>双面女王</t>
   </si>
   <si>
+    <t>yxqdb_tu_43</t>
+  </si>
+  <si>
     <t>寻宝俏丽人</t>
   </si>
   <si>
+    <t>yxqdb_tu_44</t>
+  </si>
+  <si>
     <t>蜘蛛侠</t>
   </si>
   <si>
+    <t>yxqdb_tu_45</t>
+  </si>
+  <si>
     <t>植物vs僵尸</t>
   </si>
   <si>
+    <t>yxqdb_tu_46</t>
+  </si>
+  <si>
     <t>钢铁侠</t>
   </si>
   <si>
+    <t>yxqdb_tu_47</t>
+  </si>
+  <si>
     <t>绝地求生</t>
   </si>
   <si>
+    <t>yxqdb_tu_48</t>
+  </si>
+  <si>
     <t>复仇者联盟</t>
+  </si>
+  <si>
+    <t>yxqdb_tu_49</t>
   </si>
 </sst>
 </file>
@@ -412,12 +563,12 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
+      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
@@ -888,11 +1039,8 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -1222,725 +1370,1017 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6">
-      <c r="A1" s="2" t="s">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="2" t="s">
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="2" t="s">
+      <c r="D1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="2" t="s">
+      <c r="E1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="2" t="s">
+      <c r="F1" s="1" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="2" spans="1:6">
-      <c r="A2" s="2" t="s">
+      <c r="A2" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C2" s="2" t="s">
+      <c r="C2" s="1" t="s">
         <v>7</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="E2" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="F2" s="3"/>
+      <c r="E2" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="F2" s="2" t="s">
+        <v>8</v>
+      </c>
     </row>
     <row r="3" spans="1:6">
-      <c r="A3" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="C3" s="2" t="s">
+      <c r="A3" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="D3" s="2" t="s">
+      <c r="C3" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="E3" s="2" t="s">
+      <c r="D3" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="F3" s="2"/>
+      <c r="E3" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="F3" s="1" t="s">
+        <v>13</v>
+      </c>
     </row>
     <row r="5" spans="1:6">
       <c r="A5" s="1">
         <v>1</v>
       </c>
-      <c r="B5" s="2" t="s">
-        <v>12</v>
+      <c r="B5" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="D5" s="1">
+        <v>44052</v>
       </c>
       <c r="E5" s="1">
         <v>44002</v>
       </c>
-      <c r="F5" s="1">
-        <v>0</v>
+      <c r="F5" s="1" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="6" spans="1:6">
       <c r="A6" s="1">
         <v>2</v>
       </c>
-      <c r="B6" s="2" t="s">
-        <v>13</v>
+      <c r="B6" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="D6" s="1">
+        <v>44053</v>
       </c>
       <c r="E6" s="1">
         <v>44003</v>
       </c>
-      <c r="F6" s="1">
-        <v>0</v>
+      <c r="F6" s="1" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="7" spans="1:6">
       <c r="A7" s="1">
         <v>3</v>
       </c>
-      <c r="B7" s="2" t="s">
-        <v>14</v>
+      <c r="B7" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="C7" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="D7" s="1">
+        <v>44054</v>
       </c>
       <c r="E7" s="1">
         <v>44004</v>
       </c>
-      <c r="F7" s="1">
-        <v>0</v>
+      <c r="F7" s="1" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="8" spans="1:6">
       <c r="A8" s="1">
         <v>4</v>
       </c>
-      <c r="B8" s="2" t="s">
-        <v>15</v>
+      <c r="B8" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="C8" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="D8" s="1">
+        <v>44055</v>
       </c>
       <c r="E8" s="1">
         <v>44005</v>
       </c>
-      <c r="F8" s="1">
-        <v>0</v>
+      <c r="F8" s="1" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="9" spans="1:6">
       <c r="A9" s="1">
         <v>5</v>
       </c>
-      <c r="B9" s="2" t="s">
-        <v>16</v>
+      <c r="B9" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="C9" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="D9" s="1">
+        <v>44056</v>
       </c>
       <c r="E9" s="1">
         <v>44006</v>
       </c>
-      <c r="F9" s="1">
-        <v>0</v>
+      <c r="F9" s="1" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="10" spans="1:6">
       <c r="A10" s="1">
         <v>6</v>
       </c>
-      <c r="B10" s="2" t="s">
-        <v>17</v>
+      <c r="B10" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="C10" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="D10" s="1">
+        <v>44057</v>
       </c>
       <c r="E10" s="1">
         <v>44007</v>
       </c>
-      <c r="F10" s="1">
-        <v>0</v>
+      <c r="F10" s="1" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="11" spans="1:6">
       <c r="A11" s="1">
         <v>7</v>
       </c>
-      <c r="B11" s="2" t="s">
-        <v>18</v>
+      <c r="B11" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="C11" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="D11" s="1">
+        <v>44058</v>
       </c>
       <c r="E11" s="1">
         <v>44008</v>
       </c>
-      <c r="F11" s="1">
-        <v>0</v>
+      <c r="F11" s="1" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="12" spans="1:6">
       <c r="A12" s="1">
         <v>8</v>
       </c>
-      <c r="B12" s="2" t="s">
-        <v>19</v>
+      <c r="B12" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="C12" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="D12" s="1">
+        <v>44059</v>
       </c>
       <c r="E12" s="1">
         <v>44009</v>
       </c>
-      <c r="F12" s="1">
-        <v>0</v>
+      <c r="F12" s="1" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="13" spans="1:6">
       <c r="A13" s="1">
         <v>9</v>
       </c>
-      <c r="B13" s="2" t="s">
-        <v>20</v>
+      <c r="B13" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="C13" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="D13" s="1">
+        <v>44060</v>
       </c>
       <c r="E13" s="1">
         <v>44010</v>
       </c>
-      <c r="F13" s="1">
-        <v>0</v>
+      <c r="F13" s="1" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="14" spans="1:6">
       <c r="A14" s="1">
         <v>10</v>
       </c>
-      <c r="B14" s="2" t="s">
-        <v>21</v>
+      <c r="B14" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="C14" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="D14" s="1">
+        <v>44061</v>
       </c>
       <c r="E14" s="1">
         <v>44011</v>
       </c>
-      <c r="F14" s="1">
-        <v>0</v>
+      <c r="F14" s="1" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="15" spans="1:6">
       <c r="A15" s="1">
         <v>11</v>
       </c>
-      <c r="B15" s="2" t="s">
-        <v>22</v>
+      <c r="B15" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="C15" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="D15" s="1">
+        <v>44062</v>
       </c>
       <c r="E15" s="1">
         <v>44012</v>
       </c>
-      <c r="F15" s="1">
-        <v>0</v>
+      <c r="F15" s="1" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="16" spans="1:6">
       <c r="A16" s="1">
         <v>12</v>
       </c>
-      <c r="B16" s="2" t="s">
-        <v>23</v>
+      <c r="B16" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="C16" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="D16" s="1">
+        <v>44063</v>
       </c>
       <c r="E16" s="1">
         <v>44013</v>
       </c>
-      <c r="F16" s="1">
-        <v>0</v>
+      <c r="F16" s="1" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="17" spans="1:6">
       <c r="A17" s="1">
         <v>13</v>
       </c>
-      <c r="B17" s="2" t="s">
-        <v>24</v>
+      <c r="B17" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="C17" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="D17" s="1">
+        <v>44064</v>
       </c>
       <c r="E17" s="1">
         <v>44014</v>
       </c>
-      <c r="F17" s="1">
-        <v>0</v>
+      <c r="F17" s="1" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="18" spans="1:6">
       <c r="A18" s="1">
         <v>14</v>
       </c>
-      <c r="B18" s="2" t="s">
-        <v>25</v>
+      <c r="B18" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="C18" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="D18" s="1">
+        <v>44065</v>
       </c>
       <c r="E18" s="1">
         <v>44015</v>
       </c>
-      <c r="F18" s="1">
-        <v>0</v>
+      <c r="F18" s="1" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="19" spans="1:6">
       <c r="A19" s="1">
         <v>15</v>
       </c>
-      <c r="B19" s="2" t="s">
-        <v>26</v>
+      <c r="B19" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="C19" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="D19" s="1">
+        <v>44066</v>
       </c>
       <c r="E19" s="1">
         <v>44016</v>
       </c>
-      <c r="F19" s="1">
-        <v>0</v>
+      <c r="F19" s="1" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="20" spans="1:6">
       <c r="A20" s="1">
         <v>16</v>
       </c>
-      <c r="B20" s="2" t="s">
-        <v>27</v>
+      <c r="B20" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="C20" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="D20" s="1">
+        <v>44067</v>
       </c>
       <c r="E20" s="1">
         <v>44017</v>
       </c>
-      <c r="F20" s="1">
-        <v>0</v>
+      <c r="F20" s="1" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="21" spans="1:6">
       <c r="A21" s="1">
         <v>17</v>
       </c>
-      <c r="B21" s="2" t="s">
-        <v>28</v>
+      <c r="B21" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="C21" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="D21" s="1">
+        <v>44068</v>
       </c>
       <c r="E21" s="1">
         <v>44018</v>
       </c>
-      <c r="F21" s="1">
-        <v>0</v>
+      <c r="F21" s="1" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="22" spans="1:6">
       <c r="A22" s="1">
         <v>18</v>
       </c>
-      <c r="B22" s="2" t="s">
-        <v>29</v>
+      <c r="B22" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="C22" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="D22" s="1">
+        <v>44069</v>
       </c>
       <c r="E22" s="1">
         <v>44019</v>
       </c>
-      <c r="F22" s="1">
-        <v>0</v>
+      <c r="F22" s="1" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="23" spans="1:6">
       <c r="A23" s="1">
         <v>19</v>
       </c>
-      <c r="B23" s="2" t="s">
-        <v>30</v>
+      <c r="B23" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="C23" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="D23" s="1">
+        <v>44070</v>
       </c>
       <c r="E23" s="1">
         <v>44020</v>
       </c>
-      <c r="F23" s="1">
-        <v>0</v>
+      <c r="F23" s="1" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="24" spans="1:6">
       <c r="A24" s="1">
         <v>20</v>
       </c>
-      <c r="B24" s="2" t="s">
-        <v>31</v>
+      <c r="B24" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="C24" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="D24" s="1">
+        <v>44071</v>
       </c>
       <c r="E24" s="1">
         <v>44021</v>
       </c>
-      <c r="F24" s="1">
-        <v>0</v>
+      <c r="F24" s="1" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="25" spans="1:6">
       <c r="A25" s="1">
         <v>21</v>
       </c>
-      <c r="B25" s="2" t="s">
-        <v>32</v>
+      <c r="B25" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="C25" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="D25" s="1">
+        <v>44072</v>
       </c>
       <c r="E25" s="1">
         <v>44022</v>
       </c>
-      <c r="F25" s="1">
-        <v>0</v>
+      <c r="F25" s="1" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="26" spans="1:6">
       <c r="A26" s="1">
         <v>22</v>
       </c>
-      <c r="B26" s="2" t="s">
-        <v>33</v>
+      <c r="B26" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="C26" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="D26" s="1">
+        <v>44073</v>
       </c>
       <c r="E26" s="1">
         <v>44023</v>
       </c>
-      <c r="F26" s="1">
-        <v>0</v>
+      <c r="F26" s="1" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="27" spans="1:6">
       <c r="A27" s="1">
         <v>23</v>
       </c>
-      <c r="B27" s="2" t="s">
-        <v>34</v>
+      <c r="B27" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="C27" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="D27" s="1">
+        <v>44074</v>
       </c>
       <c r="E27" s="1">
         <v>44024</v>
       </c>
-      <c r="F27" s="1">
-        <v>0</v>
+      <c r="F27" s="1" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="28" spans="1:6">
       <c r="A28" s="1">
         <v>24</v>
       </c>
-      <c r="B28" s="2" t="s">
-        <v>35</v>
+      <c r="B28" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="C28" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="D28" s="1">
+        <v>44075</v>
       </c>
       <c r="E28" s="1">
         <v>44025</v>
       </c>
-      <c r="F28" s="1">
-        <v>0</v>
+      <c r="F28" s="1" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="29" spans="1:6">
       <c r="A29" s="1">
         <v>25</v>
       </c>
-      <c r="B29" s="2" t="s">
-        <v>36</v>
+      <c r="B29" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="C29" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="D29" s="1">
+        <v>44076</v>
       </c>
       <c r="E29" s="1">
         <v>44026</v>
       </c>
-      <c r="F29" s="1">
-        <v>0</v>
+      <c r="F29" s="1" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="30" spans="1:6">
       <c r="A30" s="1">
         <v>26</v>
       </c>
-      <c r="B30" s="2" t="s">
-        <v>37</v>
+      <c r="B30" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="C30" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="D30" s="1">
+        <v>44077</v>
       </c>
       <c r="E30" s="1">
         <v>44027</v>
       </c>
-      <c r="F30" s="1">
-        <v>0</v>
+      <c r="F30" s="1" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="31" spans="1:6">
       <c r="A31" s="1">
         <v>27</v>
       </c>
-      <c r="B31" s="2" t="s">
-        <v>38</v>
+      <c r="B31" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="C31" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="D31" s="1">
+        <v>44078</v>
       </c>
       <c r="E31" s="1">
         <v>44028</v>
       </c>
-      <c r="F31" s="1">
-        <v>0</v>
+      <c r="F31" s="1" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="32" spans="1:6">
       <c r="A32" s="1">
         <v>28</v>
       </c>
-      <c r="B32" s="2" t="s">
-        <v>39</v>
+      <c r="B32" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="C32" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="D32" s="1">
+        <v>44079</v>
       </c>
       <c r="E32" s="1">
         <v>44029</v>
       </c>
-      <c r="F32" s="1">
-        <v>0</v>
+      <c r="F32" s="1" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="33" spans="1:6">
       <c r="A33" s="1">
         <v>29</v>
       </c>
-      <c r="B33" s="2" t="s">
-        <v>40</v>
+      <c r="B33" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="C33" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="D33" s="1">
+        <v>44080</v>
       </c>
       <c r="E33" s="1">
         <v>44030</v>
       </c>
-      <c r="F33" s="1">
-        <v>0</v>
+      <c r="F33" s="1" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="34" spans="1:6">
       <c r="A34" s="1">
         <v>30</v>
       </c>
-      <c r="B34" s="2" t="s">
-        <v>41</v>
+      <c r="B34" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="C34" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="D34" s="1">
+        <v>44081</v>
       </c>
       <c r="E34" s="1">
         <v>44031</v>
       </c>
-      <c r="F34" s="1">
-        <v>0</v>
+      <c r="F34" s="1" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="35" spans="1:6">
       <c r="A35" s="1">
         <v>31</v>
       </c>
-      <c r="B35" s="2" t="s">
-        <v>42</v>
+      <c r="B35" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="C35" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="D35" s="1">
+        <v>44082</v>
       </c>
       <c r="E35" s="1">
         <v>44032</v>
       </c>
-      <c r="F35" s="1">
-        <v>0</v>
+      <c r="F35" s="1" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="36" spans="1:6">
       <c r="A36" s="1">
         <v>32</v>
       </c>
-      <c r="B36" s="2" t="s">
-        <v>43</v>
+      <c r="B36" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="C36" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="D36" s="1">
+        <v>44083</v>
       </c>
       <c r="E36" s="1">
         <v>44033</v>
       </c>
-      <c r="F36" s="1">
-        <v>0</v>
+      <c r="F36" s="1" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="37" spans="1:6">
       <c r="A37" s="1">
         <v>33</v>
       </c>
-      <c r="B37" s="2" t="s">
-        <v>44</v>
+      <c r="B37" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="C37" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="D37" s="1">
+        <v>44084</v>
       </c>
       <c r="E37" s="1">
         <v>44034</v>
       </c>
-      <c r="F37" s="1">
-        <v>0</v>
+      <c r="F37" s="1" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="38" spans="1:6">
       <c r="A38" s="1">
         <v>34</v>
       </c>
-      <c r="B38" s="2" t="s">
-        <v>45</v>
+      <c r="B38" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="C38" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="D38" s="1">
+        <v>44085</v>
       </c>
       <c r="E38" s="1">
         <v>44035</v>
       </c>
-      <c r="F38" s="1">
-        <v>0</v>
+      <c r="F38" s="1" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="39" spans="1:6">
       <c r="A39" s="1">
         <v>35</v>
       </c>
-      <c r="B39" s="2" t="s">
-        <v>46</v>
+      <c r="B39" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="C39" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="D39" s="1">
+        <v>44086</v>
       </c>
       <c r="E39" s="1">
         <v>44036</v>
       </c>
-      <c r="F39" s="1">
-        <v>0</v>
+      <c r="F39" s="1" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="40" spans="1:6">
       <c r="A40" s="1">
         <v>36</v>
       </c>
-      <c r="B40" s="2" t="s">
-        <v>47</v>
+      <c r="B40" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="C40" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="D40" s="1">
+        <v>44087</v>
       </c>
       <c r="E40" s="1">
         <v>44037</v>
       </c>
-      <c r="F40" s="1">
-        <v>0</v>
+      <c r="F40" s="1" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="41" spans="1:6">
       <c r="A41" s="1">
         <v>37</v>
       </c>
-      <c r="B41" s="2" t="s">
-        <v>48</v>
+      <c r="B41" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="C41" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="D41" s="1">
+        <v>44088</v>
       </c>
       <c r="E41" s="1">
         <v>44038</v>
       </c>
-      <c r="F41" s="1">
-        <v>0</v>
+      <c r="F41" s="1" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="42" spans="1:6">
       <c r="A42" s="1">
         <v>38</v>
       </c>
-      <c r="B42" s="2" t="s">
-        <v>49</v>
+      <c r="B42" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="C42" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="D42" s="1">
+        <v>44089</v>
       </c>
       <c r="E42" s="1">
         <v>44039</v>
       </c>
-      <c r="F42" s="1">
-        <v>0</v>
+      <c r="F42" s="1" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="43" spans="1:6">
       <c r="A43" s="1">
         <v>39</v>
       </c>
-      <c r="B43" s="2" t="s">
-        <v>50</v>
+      <c r="B43" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="C43" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="D43" s="1">
+        <v>44090</v>
       </c>
       <c r="E43" s="1">
         <v>44040</v>
       </c>
-      <c r="F43" s="1">
-        <v>0</v>
+      <c r="F43" s="1" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="44" spans="1:6">
       <c r="A44" s="1">
         <v>40</v>
       </c>
-      <c r="B44" s="2" t="s">
-        <v>51</v>
+      <c r="B44" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="C44" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="D44" s="1">
+        <v>44091</v>
       </c>
       <c r="E44" s="1">
         <v>44041</v>
       </c>
-      <c r="F44" s="1">
-        <v>0</v>
+      <c r="F44" s="1" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="45" spans="1:6">
       <c r="A45" s="1">
         <v>41</v>
       </c>
-      <c r="B45" s="2" t="s">
-        <v>52</v>
+      <c r="B45" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="C45" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="D45" s="1">
+        <v>44092</v>
       </c>
       <c r="E45" s="1">
         <v>44042</v>
       </c>
-      <c r="F45" s="1">
-        <v>0</v>
+      <c r="F45" s="1" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="46" spans="1:6">
       <c r="A46" s="1">
         <v>42</v>
       </c>
-      <c r="B46" s="2" t="s">
-        <v>53</v>
+      <c r="B46" s="1" t="s">
+        <v>96</v>
+      </c>
+      <c r="C46" s="1" t="s">
+        <v>97</v>
+      </c>
+      <c r="D46" s="1">
+        <v>44093</v>
       </c>
       <c r="E46" s="1">
         <v>44043</v>
       </c>
-      <c r="F46" s="1">
-        <v>0</v>
+      <c r="F46" s="1" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="47" spans="1:6">
       <c r="A47" s="1">
         <v>43</v>
       </c>
-      <c r="B47" s="2" t="s">
-        <v>54</v>
+      <c r="B47" s="1" t="s">
+        <v>98</v>
+      </c>
+      <c r="C47" s="1" t="s">
+        <v>99</v>
+      </c>
+      <c r="D47" s="1">
+        <v>44094</v>
       </c>
       <c r="E47" s="1">
         <v>44044</v>
       </c>
-      <c r="F47" s="1">
-        <v>0</v>
+      <c r="F47" s="1" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="48" spans="1:6">
       <c r="A48" s="1">
         <v>44</v>
       </c>
-      <c r="B48" s="2" t="s">
-        <v>55</v>
+      <c r="B48" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="C48" s="1" t="s">
+        <v>101</v>
+      </c>
+      <c r="D48" s="1">
+        <v>44095</v>
       </c>
       <c r="E48" s="1">
         <v>44045</v>
       </c>
-      <c r="F48" s="1">
-        <v>0</v>
+      <c r="F48" s="1" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="49" spans="1:6">
       <c r="A49" s="1">
         <v>45</v>
       </c>
-      <c r="B49" s="2" t="s">
-        <v>56</v>
+      <c r="B49" s="1" t="s">
+        <v>102</v>
+      </c>
+      <c r="C49" s="1" t="s">
+        <v>103</v>
+      </c>
+      <c r="D49" s="1">
+        <v>44096</v>
       </c>
       <c r="E49" s="1">
         <v>44046</v>
       </c>
-      <c r="F49" s="1">
-        <v>0</v>
+      <c r="F49" s="1" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="50" spans="1:6">
       <c r="A50" s="1">
         <v>46</v>
       </c>
-      <c r="B50" s="2" t="s">
-        <v>57</v>
+      <c r="B50" s="1" t="s">
+        <v>104</v>
+      </c>
+      <c r="C50" s="1" t="s">
+        <v>105</v>
+      </c>
+      <c r="D50" s="1">
+        <v>44097</v>
       </c>
       <c r="E50" s="1">
         <v>44047</v>
       </c>
-      <c r="F50" s="1">
-        <v>0</v>
+      <c r="F50" s="1" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="51" spans="1:6">
       <c r="A51" s="1">
         <v>47</v>
       </c>
-      <c r="B51" s="2" t="s">
-        <v>58</v>
+      <c r="B51" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="C51" s="1" t="s">
+        <v>107</v>
+      </c>
+      <c r="D51" s="1">
+        <v>44098</v>
       </c>
       <c r="E51" s="1">
         <v>44048</v>
       </c>
-      <c r="F51" s="1">
-        <v>0</v>
+      <c r="F51" s="1" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="52" spans="1:6">
       <c r="A52" s="1">
         <v>48</v>
       </c>
-      <c r="B52" s="2" t="s">
-        <v>59</v>
+      <c r="B52" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="C52" s="1" t="s">
+        <v>109</v>
+      </c>
+      <c r="D52" s="1">
+        <v>44099</v>
       </c>
       <c r="E52" s="1">
         <v>44049</v>
       </c>
-      <c r="F52" s="1">
-        <v>0</v>
+      <c r="F52" s="1" t="b">
+        <v>1</v>
       </c>
     </row>
   </sheetData>

--- a/hall/resources/sample/UpcomingMobileGame.xlsx
+++ b/hall/resources/sample/UpcomingMobileGame.xlsx
@@ -404,7 +404,7 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="23">
+  <fonts count="24">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -415,6 +415,12 @@
     <font>
       <sz val="11"/>
       <color theme="1"/>
+      <name val="微软雅黑"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
       <name val="微软雅黑"/>
       <charset val="134"/>
     </font>
@@ -563,12 +569,12 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
-      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
@@ -909,137 +915,137 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="2">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="3">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="3">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="4">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="5">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="6">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="5">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="5" borderId="7">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="8">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="9">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="6" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="7" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="8" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="9" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="10" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="11" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="12" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="13" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="14" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="15" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="16" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="17" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="18" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="19" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="20" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="21" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="22" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="23" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="24" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="25" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="26" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="27" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="28" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="29" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="30" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="31" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="32" borderId="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="3">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="4">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="5">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="6">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="4" borderId="5">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="5" borderId="7">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="8">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="9">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="6" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="7" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="8" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="9" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="10" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="11" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="12" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="13" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="14" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="15" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="16" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="17" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="18" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="19" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="20" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="21" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="22" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="23" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="24" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="25" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="26" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="27" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="28" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="29" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="30" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="31" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="32" borderId="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -1047,6 +1053,9 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -1439,8 +1448,8 @@
       <c r="E5" s="1">
         <v>44002</v>
       </c>
-      <c r="F5" s="1" t="b">
-        <v>1</v>
+      <c r="F5" s="3" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="6" spans="1:6">
@@ -1459,8 +1468,8 @@
       <c r="E6" s="1">
         <v>44003</v>
       </c>
-      <c r="F6" s="1" t="b">
-        <v>1</v>
+      <c r="F6" s="3" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="7" spans="1:6">
@@ -1479,8 +1488,8 @@
       <c r="E7" s="1">
         <v>44004</v>
       </c>
-      <c r="F7" s="1" t="b">
-        <v>1</v>
+      <c r="F7" s="3" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="8" spans="1:6">
@@ -1499,8 +1508,8 @@
       <c r="E8" s="1">
         <v>44005</v>
       </c>
-      <c r="F8" s="1" t="b">
-        <v>1</v>
+      <c r="F8" s="3" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="9" spans="1:6">
@@ -1539,8 +1548,8 @@
       <c r="E10" s="1">
         <v>44007</v>
       </c>
-      <c r="F10" s="1" t="b">
-        <v>1</v>
+      <c r="F10" s="3" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="11" spans="1:6">
@@ -1559,8 +1568,8 @@
       <c r="E11" s="1">
         <v>44008</v>
       </c>
-      <c r="F11" s="1" t="b">
-        <v>1</v>
+      <c r="F11" s="3" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="12" spans="1:6">
@@ -1579,8 +1588,8 @@
       <c r="E12" s="1">
         <v>44009</v>
       </c>
-      <c r="F12" s="1" t="b">
-        <v>1</v>
+      <c r="F12" s="3" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="13" spans="1:6">
@@ -1599,8 +1608,8 @@
       <c r="E13" s="1">
         <v>44010</v>
       </c>
-      <c r="F13" s="1" t="b">
-        <v>1</v>
+      <c r="F13" s="3" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="14" spans="1:6">
@@ -1619,8 +1628,8 @@
       <c r="E14" s="1">
         <v>44011</v>
       </c>
-      <c r="F14" s="1" t="b">
-        <v>1</v>
+      <c r="F14" s="3" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="15" spans="1:6">
@@ -1639,8 +1648,8 @@
       <c r="E15" s="1">
         <v>44012</v>
       </c>
-      <c r="F15" s="1" t="b">
-        <v>1</v>
+      <c r="F15" s="3" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="16" spans="1:6">
@@ -1659,8 +1668,8 @@
       <c r="E16" s="1">
         <v>44013</v>
       </c>
-      <c r="F16" s="1" t="b">
-        <v>1</v>
+      <c r="F16" s="3" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="17" spans="1:6">
@@ -1739,8 +1748,8 @@
       <c r="E20" s="1">
         <v>44017</v>
       </c>
-      <c r="F20" s="1" t="b">
-        <v>1</v>
+      <c r="F20" s="3" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="21" spans="1:6">
@@ -1859,8 +1868,8 @@
       <c r="E26" s="1">
         <v>44023</v>
       </c>
-      <c r="F26" s="1" t="b">
-        <v>1</v>
+      <c r="F26" s="3" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="27" spans="1:6">
@@ -2279,8 +2288,8 @@
       <c r="E47" s="1">
         <v>44044</v>
       </c>
-      <c r="F47" s="1" t="b">
-        <v>1</v>
+      <c r="F47" s="3" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="48" spans="1:6">
